--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][CI]Aggregated_U_test.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][CI]Aggregated_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_P2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_P1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_P1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Median_P2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median_difference_P2_minus_P1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -495,40 +507,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C2" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D2" t="n">
-        <v>8.812689854699178</v>
+        <v>8.681416526644965</v>
       </c>
       <c r="E2" t="n">
-        <v>14.29721593130561</v>
+        <v>13.97753819385776</v>
       </c>
       <c r="F2" t="n">
-        <v>4.021128608176064</v>
+        <v>4.000089800251686</v>
       </c>
       <c r="G2" t="n">
-        <v>3.447137552357112</v>
+        <v>3.299627836502728</v>
       </c>
       <c r="H2" t="n">
-        <v>8.949106959750324</v>
+        <v>8.812549929289855</v>
       </c>
       <c r="I2" t="n">
-        <v>14.3086852631912</v>
+        <v>14.06732068881405</v>
       </c>
       <c r="J2" t="n">
-        <v>5.359578303440877</v>
+        <v>5.254770759524195</v>
       </c>
       <c r="K2" t="n">
-        <v>84110</v>
+        <v>72712</v>
       </c>
       <c r="L2" t="n">
-        <v>1.540807470021926e-115</v>
+        <v>4.06468957371871e-103</v>
       </c>
       <c r="M2" t="n">
-        <v>6.163229880087706e-115</v>
+        <v>1.625875829487484e-102</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -541,40 +553,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C3" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D3" t="n">
-        <v>70.20167487442151</v>
+        <v>70.2369722645614</v>
       </c>
       <c r="E3" t="n">
-        <v>78.61028696259802</v>
+        <v>79.11736056195366</v>
       </c>
       <c r="F3" t="n">
-        <v>11.21381392129973</v>
+        <v>11.22458757169816</v>
       </c>
       <c r="G3" t="n">
-        <v>7.690782147463326</v>
+        <v>7.179065472820112</v>
       </c>
       <c r="H3" t="n">
         <v>70.6262858755511</v>
       </c>
       <c r="I3" t="n">
-        <v>78.45964744403875</v>
+        <v>78.71524750455694</v>
       </c>
       <c r="J3" t="n">
-        <v>7.833361568487646</v>
+        <v>8.088961629005837</v>
       </c>
       <c r="K3" t="n">
-        <v>151336</v>
+        <v>121346</v>
       </c>
       <c r="L3" t="n">
-        <v>3.502446414313814e-48</v>
+        <v>2.78838259212539e-49</v>
       </c>
       <c r="M3" t="n">
-        <v>1.400978565725526e-47</v>
+        <v>1.115353036850156e-48</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -587,40 +599,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C4" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D4" t="n">
-        <v>11.29708099430695</v>
+        <v>11.16394068375159</v>
       </c>
       <c r="E4" t="n">
-        <v>17.07456143766741</v>
+        <v>16.70502907146563</v>
       </c>
       <c r="F4" t="n">
-        <v>3.717876687534991</v>
+        <v>3.690045282573553</v>
       </c>
       <c r="G4" t="n">
-        <v>3.526251918279216</v>
+        <v>3.343088303370136</v>
       </c>
       <c r="H4" t="n">
-        <v>11.3230470745133</v>
+        <v>11.1918755383568</v>
       </c>
       <c r="I4" t="n">
-        <v>17.0689092560013</v>
+        <v>16.84727952443105</v>
       </c>
       <c r="J4" t="n">
-        <v>5.745862181488</v>
+        <v>5.655403986074251</v>
       </c>
       <c r="K4" t="n">
-        <v>73107</v>
+        <v>63782</v>
       </c>
       <c r="L4" t="n">
-        <v>2.221078000081962e-129</v>
+        <v>3.496893572353514e-115</v>
       </c>
       <c r="M4" t="n">
-        <v>8.884312000327849e-129</v>
+        <v>1.398757428941405e-114</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -633,40 +645,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C5" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D5" t="n">
-        <v>95.36227972754909</v>
+        <v>95.49133974038193</v>
       </c>
       <c r="E5" t="n">
-        <v>79.49083473107227</v>
+        <v>79.7701585016089</v>
       </c>
       <c r="F5" t="n">
-        <v>26.03549608471826</v>
+        <v>26.09376692931776</v>
       </c>
       <c r="G5" t="n">
-        <v>30.0105254730432</v>
+        <v>29.93068471048002</v>
       </c>
       <c r="H5" t="n">
-        <v>98.15268442497396</v>
+        <v>98.04566279639725</v>
       </c>
       <c r="I5" t="n">
-        <v>80.8606565161448</v>
+        <v>82.09190306966485</v>
       </c>
       <c r="J5" t="n">
-        <v>-17.29202790882916</v>
+        <v>-15.9537597267324</v>
       </c>
       <c r="K5" t="n">
-        <v>353140</v>
+        <v>295892</v>
       </c>
       <c r="L5" t="n">
-        <v>1.635521509067439e-24</v>
+        <v>4.110677203695538e-22</v>
       </c>
       <c r="M5" t="n">
-        <v>6.542086036269754e-24</v>
+        <v>1.644270881478215e-21</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
